--- a/Личное/Липидка.xlsx
+++ b/Личное/Липидка.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARTEM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\c_verilog\Личное\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43FC91-2A99-4D9E-BE08-3CD671B2B83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB835A8-CA4C-47A4-AE41-D603BFB694ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19320" yWindow="2265" windowWidth="17415" windowHeight="15870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Потери жидкости</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Какие овощи</t>
   </si>
   <si>
-    <t>Томат, пекинская капуста</t>
-  </si>
-  <si>
     <t>03.04 не пил изотоник</t>
   </si>
   <si>
@@ -112,6 +109,15 @@
   </si>
   <si>
     <t>115-125</t>
+  </si>
+  <si>
+    <t>Кабачковая икра</t>
+  </si>
+  <si>
+    <t>Отруби</t>
+  </si>
+  <si>
+    <t>Томат, пекин. кап., свекла, отруби</t>
   </si>
 </sst>
 </file>
@@ -119,8 +125,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -320,9 +326,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -331,12 +337,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -349,7 +355,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -371,6 +377,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -673,7 +688,7 @@
       <c r="K1" s="26"/>
       <c r="L1" s="27"/>
       <c r="O1" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P1" s="13"/>
       <c r="Q1" s="14"/>
@@ -726,22 +741,22 @@
         <v>8</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="J3" s="9">
-        <v>5.4</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="O3" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P3" s="17"/>
       <c r="Q3" s="18"/>
@@ -755,11 +770,11 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="3"/>
       <c r="O4" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P4" s="20"/>
       <c r="Q4" s="21"/>
@@ -773,11 +788,11 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="O5" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P5" s="20"/>
       <c r="Q5" s="21"/>
@@ -791,11 +806,11 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
       <c r="K6" s="3"/>
       <c r="O6" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P6" s="20"/>
       <c r="Q6" s="21"/>
@@ -809,11 +824,11 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="3"/>
       <c r="O7" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P7" s="23"/>
       <c r="Q7" s="24"/>
@@ -827,8 +842,8 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -840,11 +855,11 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="3"/>
       <c r="O9" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P9" s="26"/>
       <c r="Q9" s="27"/>
@@ -858,11 +873,11 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="3"/>
       <c r="O10" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="28" t="s">
@@ -878,10 +893,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="3"/>
-      <c r="O11" t="s">
+      <c r="O11" s="32" t="s">
         <v>12</v>
       </c>
       <c r="P11" s="15"/>
@@ -898,10 +913,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="3"/>
-      <c r="O12" t="s">
+      <c r="O12" s="32" t="s">
         <v>13</v>
       </c>
       <c r="Q12" s="4">
@@ -917,10 +932,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="3"/>
-      <c r="O13" t="s">
+      <c r="O13" s="32" t="s">
         <v>14</v>
       </c>
       <c r="Q13" s="4">
@@ -936,10 +951,15 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="3"/>
-      <c r="O14" s="4"/>
+      <c r="O14" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="34">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -950,10 +970,15 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="3"/>
-      <c r="O15" s="4"/>
+      <c r="O15" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="34">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -964,10 +989,10 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="3"/>
-      <c r="O16" s="4"/>
+      <c r="O16" s="33"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -978,10 +1003,10 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="3"/>
-      <c r="O17" s="4"/>
+      <c r="O17" s="33"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -992,10 +1017,10 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="3"/>
-      <c r="O18" s="4"/>
+      <c r="O18" s="33"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -1006,10 +1031,10 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="3"/>
-      <c r="O19" s="4"/>
+      <c r="O19" s="33"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -1020,10 +1045,10 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="3"/>
-      <c r="O20" s="4"/>
+      <c r="O20" s="33"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -1034,10 +1059,10 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="3"/>
-      <c r="O21" s="4"/>
+      <c r="O21" s="33"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
@@ -1048,10 +1073,10 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="3"/>
-      <c r="O22" s="4"/>
+      <c r="O22" s="33"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1062,10 +1087,10 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="3"/>
-      <c r="O23" s="4"/>
+      <c r="O23" s="33"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -1076,10 +1101,10 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
       <c r="K24" s="3"/>
-      <c r="O24" s="4"/>
+      <c r="O24" s="33"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -1090,10 +1115,10 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="3"/>
-      <c r="O25" s="4"/>
+      <c r="O25" s="33"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -1104,10 +1129,10 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="3"/>
-      <c r="O26" s="4"/>
+      <c r="O26" s="33"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -1118,10 +1143,10 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="3"/>
-      <c r="O27" s="4"/>
+      <c r="O27" s="33"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -1132,10 +1157,10 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="3"/>
-      <c r="O28" s="4"/>
+      <c r="O28" s="33"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -1146,10 +1171,10 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="3"/>
-      <c r="O29" s="4"/>
+      <c r="O29" s="33"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -1160,10 +1185,10 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="3"/>
-      <c r="O30" s="4"/>
+      <c r="O30" s="33"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -1174,10 +1199,10 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="3"/>
-      <c r="O31" s="4"/>
+      <c r="O31" s="33"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
@@ -1188,10 +1213,10 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="3"/>
-      <c r="O32" s="4"/>
+      <c r="O32" s="33"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
@@ -1202,10 +1227,10 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="3"/>
-      <c r="O33" s="4"/>
+      <c r="O33" s="33"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
@@ -1216,10 +1241,10 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
       <c r="K34" s="3"/>
-      <c r="O34" s="4"/>
+      <c r="O34" s="33"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
@@ -1230,10 +1255,10 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
       <c r="K35" s="3"/>
-      <c r="O35" s="4"/>
+      <c r="O35" s="33"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
@@ -1244,10 +1269,10 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
       <c r="K36" s="3"/>
-      <c r="O36" s="4"/>
+      <c r="O36" s="33"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
@@ -1258,10 +1283,10 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="3"/>
-      <c r="O37" s="4"/>
+      <c r="O37" s="33"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>

--- a/Личное/Липидка.xlsx
+++ b/Личное/Липидка.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\c_verilog\Личное\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB835A8-CA4C-47A4-AE41-D603BFB694ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19320" yWindow="2265" windowWidth="17415" windowHeight="15870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19320" yWindow="2265" windowWidth="17415" windowHeight="15870"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Потери жидкости</t>
   </si>
@@ -118,12 +112,15 @@
   </si>
   <si>
     <t>Томат, пекин. кап., свекла, отруби</t>
+  </si>
+  <si>
+    <t>Томат, пекин. кап.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -326,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,6 +382,12 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,14 +661,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -762,17 +765,27 @@
       <c r="Q3" s="18"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="3"/>
+      <c r="A4" s="7">
+        <v>45751</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="35">
+        <v>320</v>
+      </c>
+      <c r="J4" s="35">
+        <v>4.3</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
       <c r="O4" s="19" t="s">
         <v>17</v>
       </c>
@@ -790,7 +803,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="36"/>
       <c r="O5" s="19" t="s">
         <v>18</v>
       </c>
@@ -808,7 +821,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="36"/>
       <c r="O6" s="19" t="s">
         <v>19</v>
       </c>
@@ -826,7 +839,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="36"/>
       <c r="O7" s="22" t="s">
         <v>20</v>
       </c>
@@ -844,7 +857,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="36"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
@@ -857,7 +870,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="36"/>
       <c r="O9" s="25" t="s">
         <v>22</v>
       </c>
@@ -875,7 +888,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="36"/>
       <c r="O10" s="28" t="s">
         <v>23</v>
       </c>
@@ -895,7 +908,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="36"/>
       <c r="O11" s="32" t="s">
         <v>12</v>
       </c>
@@ -915,7 +928,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="36"/>
       <c r="O12" s="32" t="s">
         <v>13</v>
       </c>
@@ -934,7 +947,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="36"/>
       <c r="O13" s="32" t="s">
         <v>14</v>
       </c>
@@ -953,7 +966,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="36"/>
       <c r="O14" s="33" t="s">
         <v>25</v>
       </c>
@@ -972,7 +985,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="36"/>
       <c r="O15" s="33" t="s">
         <v>26</v>
       </c>
@@ -991,7 +1004,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="36"/>
       <c r="O16" s="33"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1005,7 +1018,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="36"/>
       <c r="O17" s="33"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1019,7 +1032,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="36"/>
       <c r="O18" s="33"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1033,7 +1046,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="36"/>
       <c r="O19" s="33"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1047,7 +1060,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="36"/>
       <c r="O20" s="33"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1061,7 +1074,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="36"/>
       <c r="O21" s="33"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1075,7 +1088,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="3"/>
+      <c r="K22" s="36"/>
       <c r="O22" s="33"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1089,7 +1102,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="36"/>
       <c r="O23" s="33"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1103,7 +1116,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="3"/>
+      <c r="K24" s="36"/>
       <c r="O24" s="33"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1117,7 +1130,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-      <c r="K25" s="3"/>
+      <c r="K25" s="36"/>
       <c r="O25" s="33"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1131,7 +1144,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="3"/>
+      <c r="K26" s="36"/>
       <c r="O26" s="33"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -1145,7 +1158,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="36"/>
       <c r="O27" s="33"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -1159,7 +1172,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="3"/>
+      <c r="K28" s="36"/>
       <c r="O28" s="33"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1173,7 +1186,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="3"/>
+      <c r="K29" s="36"/>
       <c r="O29" s="33"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -1187,7 +1200,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="3"/>
+      <c r="K30" s="36"/>
       <c r="O30" s="33"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -1201,7 +1214,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-      <c r="K31" s="3"/>
+      <c r="K31" s="36"/>
       <c r="O31" s="33"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -1215,7 +1228,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="3"/>
+      <c r="K32" s="36"/>
       <c r="O32" s="33"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1229,7 +1242,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="3"/>
+      <c r="K33" s="36"/>
       <c r="O33" s="33"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -1243,7 +1256,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="36"/>
       <c r="O34" s="33"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -1257,7 +1270,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="3"/>
+      <c r="K35" s="36"/>
       <c r="O35" s="33"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">

--- a/Личное/Липидка.xlsx
+++ b/Личное/Липидка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\c_verilog\Личное\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB835A8-CA4C-47A4-AE41-D603BFB694ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC58E892-250A-4754-8B2B-ACB96046103D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19320" yWindow="2265" windowWidth="17415" windowHeight="15870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
   <si>
     <t>Потери жидкости</t>
   </si>
@@ -118,6 +118,90 @@
   </si>
   <si>
     <t>Томат, пекин. кап., свекла, отруби</t>
+  </si>
+  <si>
+    <t>Б</t>
+  </si>
+  <si>
+    <t>Ж</t>
+  </si>
+  <si>
+    <t>У</t>
+  </si>
+  <si>
+    <t>Ккал</t>
+  </si>
+  <si>
+    <t>40 мин.</t>
+  </si>
+  <si>
+    <t>30 мин.</t>
+  </si>
+  <si>
+    <t>31 мин.</t>
+  </si>
+  <si>
+    <t>Время</t>
+  </si>
+  <si>
+    <t>АД</t>
+  </si>
+  <si>
+    <t>Давл.</t>
+  </si>
+  <si>
+    <t>127/90</t>
+  </si>
+  <si>
+    <t>130/80</t>
+  </si>
+  <si>
+    <t>120/80</t>
+  </si>
+  <si>
+    <t>Пекин. кап, кабач. икра</t>
+  </si>
+  <si>
+    <t>Авокадо</t>
+  </si>
+  <si>
+    <t>Кукуруза</t>
+  </si>
+  <si>
+    <t>Айсберг</t>
+  </si>
+  <si>
+    <t>Том, авок, огур, айс, кукур.</t>
+  </si>
+  <si>
+    <t>120/70</t>
+  </si>
+  <si>
+    <t>кукур, авок, пекин кап</t>
+  </si>
+  <si>
+    <t>кукур, пекин</t>
+  </si>
+  <si>
+    <t>зелень, фасоль</t>
+  </si>
+  <si>
+    <t>салат</t>
+  </si>
+  <si>
+    <t>фасоль</t>
+  </si>
+  <si>
+    <t>Яблоко</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Морковь </t>
+  </si>
+  <si>
+    <t>морковь, яблоко</t>
+  </si>
+  <si>
+    <t>Среднее</t>
   </si>
 </sst>
 </file>
@@ -137,7 +221,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,8 +252,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -322,11 +412,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,19 +625,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -380,12 +644,265 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -401,6 +918,2344 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Ж</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>dd/mm/yy;@</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45753</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$W$3:$W$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>73.77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74.22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>83.83</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64.27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99.13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>85.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>97.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>71.89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>98.54</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3751-4980-B073-6962CE6D78B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>У</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>dd/mm/yy;@</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45753</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$X$3:$X$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>400.52</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>478.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>506.54</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>418.41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>449.58</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>439.95</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>408.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>517.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>489.11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>563.92999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3751-4980-B073-6962CE6D78B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Б</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>dd/mm/yy;@</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45753</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Y$3:$Y$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>203.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>205.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>213.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>209.91</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>201.83</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>234.71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>211.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>209.55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>212.22</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>201.98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3751-4980-B073-6962CE6D78B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1321674880"/>
+        <c:axId val="1321675296"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>ккал</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>dd/mm/yy;@</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45753</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Z$3:$Z$13</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>3117</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3388</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3741</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3264</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3628</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3798</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3293</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3774</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3466</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4184</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3751-4980-B073-6962CE6D78B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1321774544"/>
+        <c:axId val="1334573392"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1321674880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd/mm/yy;@" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321675296"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="days"/>
+        <c:minorUnit val="1"/>
+        <c:minorTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1321675296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321674880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1334573392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321774544"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dateAx>
+        <c:axId val="1321774544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd/mm/yy;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1334573392"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>вес</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$3:$A$13</c:f>
+              <c:numCache>
+                <c:formatCode>dd/mm/yy;@</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45753</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45755</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45756</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45758</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45760</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$B$3:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>106.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>104.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EA33-4A4C-A449-54EAD8FA4765}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="1359333920"/>
+        <c:axId val="1359334336"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1359333920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd/mm/yy;@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1359334336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1359334336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1359333920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22AA9F37-1CC0-4E88-B6FB-FE3A650F2711}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>42861</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>561974</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE04BE1-D315-4167-BC4E-5DFFD93E41AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -666,34 +3521,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="28"/>
+    <col min="14" max="17" width="9.140625" style="30"/>
+    <col min="19" max="19" width="9.140625" style="89"/>
+    <col min="20" max="22" width="9.140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="F1" s="29" t="s">
+      <c r="B1" s="27"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="I1" s="25" t="s">
+      <c r="G1" s="13"/>
+      <c r="I1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="27"/>
-      <c r="O1" s="12" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="23"/>
+      <c r="N1" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="43"/>
+      <c r="S1" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="14"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="13"/>
+      <c r="V1"/>
+      <c r="W1" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" s="43" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -718,438 +3596,981 @@
       <c r="J2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="28" t="s">
         <v>15</v>
       </c>
+      <c r="N2" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="W2" s="129">
+        <f>AVERAGE(W3:W52)</f>
+        <v>83.144999999999996</v>
+      </c>
+      <c r="X2" s="129">
+        <f t="shared" ref="X2:Z2" si="0">AVERAGE(X3:X52)</f>
+        <v>467.23999999999995</v>
+      </c>
+      <c r="Y2" s="129">
+        <f t="shared" si="0"/>
+        <v>210.48599999999996</v>
+      </c>
+      <c r="Z2" s="130">
+        <f t="shared" si="0"/>
+        <v>3565.3</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>45750</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="31">
         <v>106.3</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="31">
         <v>105.85</v>
       </c>
-      <c r="D3" s="8">
-        <f>B3-C3</f>
-        <v>0.45000000000000284</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="96">
+        <f>C3-B3</f>
+        <v>-0.45000000000000284</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9">
+      <c r="H3" s="32"/>
+      <c r="I3" s="32">
         <v>477</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="32">
         <v>9.6999999999999993</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="O3" s="16" t="s">
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="S3" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="18"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="16"/>
+      <c r="V3"/>
+      <c r="W3" s="99">
+        <v>73.77</v>
+      </c>
+      <c r="X3" s="99">
+        <v>400.52</v>
+      </c>
+      <c r="Y3" s="99">
+        <v>203.1</v>
+      </c>
+      <c r="Z3" s="118">
+        <v>3117</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="3"/>
-      <c r="O4" s="19" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>45751</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="37">
+        <v>232</v>
+      </c>
+      <c r="J4" s="37">
+        <v>5.2</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="S4" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="21"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="18"/>
+      <c r="V4"/>
+      <c r="W4" s="100">
+        <v>74.22</v>
+      </c>
+      <c r="X4" s="100">
+        <v>478.66</v>
+      </c>
+      <c r="Y4" s="100">
+        <v>205.9</v>
+      </c>
+      <c r="Z4" s="119">
+        <v>3388</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>45752</v>
+      </c>
+      <c r="B5" s="36">
+        <v>105.5</v>
+      </c>
+      <c r="C5" s="36">
+        <v>106.25</v>
+      </c>
+      <c r="D5" s="97">
+        <f>C5-B5</f>
+        <v>0.75</v>
+      </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>24</v>
+      </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
-      <c r="O5" s="19" t="s">
+      <c r="I5" s="4">
+        <v>367</v>
+      </c>
+      <c r="J5" s="4">
+        <v>5.45</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="40">
+        <v>0.91111111111111109</v>
+      </c>
+      <c r="S5" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="21"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="18"/>
+      <c r="V5"/>
+      <c r="W5" s="99">
+        <v>83.83</v>
+      </c>
+      <c r="X5" s="99">
+        <v>506.54</v>
+      </c>
+      <c r="Y5" s="99">
+        <v>213.91</v>
+      </c>
+      <c r="Z5" s="118">
+        <v>3741</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
-      <c r="O6" s="19" t="s">
+    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48">
+        <v>45753</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="35">
+        <v>87</v>
+      </c>
+      <c r="J6" s="35">
+        <v>1.879</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="45">
+        <v>0.62916666666666665</v>
+      </c>
+      <c r="P6" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="45">
+        <v>0.92361111111111116</v>
+      </c>
+      <c r="S6" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="21"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="18"/>
+      <c r="V6"/>
+      <c r="W6" s="101">
+        <v>83</v>
+      </c>
+      <c r="X6" s="101">
+        <v>418.41</v>
+      </c>
+      <c r="Y6" s="101">
+        <v>209.91</v>
+      </c>
+      <c r="Z6" s="120">
+        <v>3264</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="O7" s="22" t="s">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="50">
+        <v>45754</v>
+      </c>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="53">
+        <v>170</v>
+      </c>
+      <c r="J7" s="53">
+        <v>5.44</v>
+      </c>
+      <c r="K7" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="57"/>
+      <c r="S7" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="24"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="20"/>
+      <c r="V7"/>
+      <c r="W7" s="102">
+        <v>64.27</v>
+      </c>
+      <c r="X7" s="103">
+        <v>449.58</v>
+      </c>
+      <c r="Y7" s="103">
+        <v>201.83</v>
+      </c>
+      <c r="Z7" s="121">
+        <v>3628</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="58">
+        <v>45755</v>
+      </c>
+      <c r="B8" s="8">
+        <v>105.5</v>
+      </c>
+      <c r="C8" s="8">
+        <v>105.5</v>
+      </c>
+      <c r="D8" s="98">
+        <f>C8-B8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="37">
+        <v>0</v>
+      </c>
+      <c r="J8" s="37"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="59"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8" s="104">
+        <v>99.13</v>
+      </c>
+      <c r="X8" s="100">
+        <v>439.95</v>
+      </c>
+      <c r="Y8" s="100">
+        <v>234.71</v>
+      </c>
+      <c r="Z8" s="122">
+        <v>3798</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="3"/>
-      <c r="O9" s="25" t="s">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="58">
+        <v>45756</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61">
+        <v>250</v>
+      </c>
+      <c r="J9" s="61">
+        <v>3.2</v>
+      </c>
+      <c r="K9" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="64"/>
+      <c r="S9" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="27"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="23"/>
+      <c r="V9"/>
+      <c r="W9" s="105">
+        <v>85.5</v>
+      </c>
+      <c r="X9" s="106">
+        <v>408.4</v>
+      </c>
+      <c r="Y9" s="106">
+        <v>211.75</v>
+      </c>
+      <c r="Z9" s="123">
+        <v>3293</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="3"/>
-      <c r="O10" s="28" t="s">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="58">
+        <v>45757</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="37">
+        <v>220</v>
+      </c>
+      <c r="J10" s="37">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="59"/>
+      <c r="S10" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="28" t="s">
+      <c r="T10" s="14"/>
+      <c r="U10" s="24" t="s">
         <v>9</v>
       </c>
+      <c r="V10"/>
+      <c r="W10" s="104">
+        <v>97.3</v>
+      </c>
+      <c r="X10" s="100">
+        <v>517.29999999999995</v>
+      </c>
+      <c r="Y10" s="100">
+        <v>209.55</v>
+      </c>
+      <c r="Z10" s="122">
+        <v>3774</v>
+      </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="3"/>
-      <c r="O11" s="32" t="s">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="58">
+        <v>45758</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61">
+        <v>100</v>
+      </c>
+      <c r="J11" s="61">
+        <v>1</v>
+      </c>
+      <c r="K11" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="64"/>
+      <c r="S11" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11"/>
+      <c r="U11" s="29">
+        <v>22</v>
+      </c>
+      <c r="V11"/>
+      <c r="W11" s="105">
+        <v>71.89</v>
+      </c>
+      <c r="X11" s="106">
+        <v>489.11</v>
+      </c>
+      <c r="Y11" s="106">
+        <v>212.22</v>
+      </c>
+      <c r="Z11" s="123">
+        <v>3466</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="58">
+        <v>45759</v>
+      </c>
+      <c r="B12" s="8">
+        <v>104.95</v>
+      </c>
+      <c r="C12" s="8">
+        <v>105.55</v>
+      </c>
+      <c r="D12" s="98">
+        <f>C12-B12</f>
+        <v>0.59999999999999432</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="37">
+        <v>100</v>
+      </c>
+      <c r="J12" s="37">
+        <v>2.64</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="59"/>
+      <c r="S12" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="U12" s="30">
+        <v>6.7</v>
+      </c>
+      <c r="V12"/>
+      <c r="W12" s="104">
+        <v>98.54</v>
+      </c>
+      <c r="X12" s="100">
+        <v>563.92999999999995</v>
+      </c>
+      <c r="Y12" s="100">
+        <v>201.98</v>
+      </c>
+      <c r="Z12" s="122">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="65">
+        <v>45760</v>
+      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="87">
+        <v>0.46805555555555556</v>
+      </c>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="72"/>
+      <c r="S13" s="89" t="s">
+        <v>53</v>
+      </c>
+      <c r="U13" s="30">
+        <v>2.8</v>
+      </c>
+      <c r="V13"/>
+      <c r="W13" s="107"/>
+      <c r="X13" s="108"/>
+      <c r="Y13" s="108"/>
+      <c r="Z13" s="124"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="50">
+        <v>45761</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="79"/>
+      <c r="S14" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="U14" s="30">
+        <v>2.5</v>
+      </c>
+      <c r="V14"/>
+      <c r="W14" s="102"/>
+      <c r="X14" s="103"/>
+      <c r="Y14" s="103"/>
+      <c r="Z14" s="121"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="58">
+        <v>45762</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="64"/>
+      <c r="S15" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="U15" s="30">
+        <v>2.4</v>
+      </c>
+      <c r="V15"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="100"/>
+      <c r="Y15" s="100"/>
+      <c r="Z15" s="122"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="58">
+        <v>45763</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="59"/>
+      <c r="S16" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16"/>
+      <c r="U16" s="29">
+        <v>2</v>
+      </c>
+      <c r="W16" s="109"/>
+      <c r="X16" s="110"/>
+      <c r="Y16" s="110"/>
+      <c r="Z16" s="125"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" s="58">
+        <v>45764</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="64"/>
+      <c r="S17" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="4">
+      <c r="T17" s="14"/>
+      <c r="U17" s="4">
         <v>1.7</v>
       </c>
+      <c r="W17" s="111"/>
+      <c r="X17" s="112"/>
+      <c r="Y17" s="112"/>
+      <c r="Z17" s="126"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="3"/>
-      <c r="O12" s="32" t="s">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18" s="58">
+        <v>45765</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="59"/>
+      <c r="S18" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="U18" s="30">
+        <v>1.2</v>
+      </c>
+      <c r="W18" s="109"/>
+      <c r="X18" s="110"/>
+      <c r="Y18" s="110"/>
+      <c r="Z18" s="125"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="58">
+        <v>45766</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="64"/>
+      <c r="S19" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="T19"/>
+      <c r="U19" s="4">
         <v>1</v>
       </c>
+      <c r="W19" s="111"/>
+      <c r="X19" s="112"/>
+      <c r="Y19" s="112"/>
+      <c r="Z19" s="126"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="3"/>
-      <c r="O13" s="32" t="s">
+    <row r="20" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="65">
+        <v>45767</v>
+      </c>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="86"/>
+      <c r="S20" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="T20"/>
+      <c r="U20" s="4">
         <v>0.7</v>
       </c>
+      <c r="W20" s="113"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="127"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="3"/>
-      <c r="O14" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="34">
-        <v>2</v>
-      </c>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" s="50">
+        <v>45768</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="57"/>
+      <c r="W21" s="115"/>
+      <c r="X21" s="116"/>
+      <c r="Y21" s="116"/>
+      <c r="Z21" s="128"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="3"/>
-      <c r="O15" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="34">
-        <v>22</v>
-      </c>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" s="58">
+        <v>45769</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="59"/>
+      <c r="W22" s="111"/>
+      <c r="X22" s="112"/>
+      <c r="Y22" s="112"/>
+      <c r="Z22" s="126"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
-      <c r="O16" s="33"/>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="58">
+        <v>45770</v>
+      </c>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="64"/>
+      <c r="W23" s="109"/>
+      <c r="X23" s="110"/>
+      <c r="Y23" s="110"/>
+      <c r="Z23" s="125"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="3"/>
-      <c r="O17" s="33"/>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" s="58">
+        <v>45771</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="59"/>
+      <c r="W24" s="111"/>
+      <c r="X24" s="112"/>
+      <c r="Y24" s="112"/>
+      <c r="Z24" s="126"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="3"/>
-      <c r="O18" s="33"/>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" s="58">
+        <v>45772</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="64"/>
+      <c r="W25" s="109"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="110"/>
+      <c r="Z25" s="125"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="3"/>
-      <c r="O19" s="33"/>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="58">
+        <v>45773</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="37"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="59"/>
+      <c r="W26" s="111"/>
+      <c r="X26" s="112"/>
+      <c r="Y26" s="112"/>
+      <c r="Z26" s="126"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="3"/>
-      <c r="O20" s="33"/>
+    <row r="27" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="65">
+        <v>45774</v>
+      </c>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="72"/>
+      <c r="W27" s="113"/>
+      <c r="X27" s="114"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="127"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="3"/>
-      <c r="O21" s="33"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="3"/>
-      <c r="O22" s="33"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="3"/>
-      <c r="O23" s="33"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="3"/>
-      <c r="O24" s="33"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="3"/>
-      <c r="O25" s="33"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="3"/>
-      <c r="O26" s="33"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="3"/>
-      <c r="O27" s="33"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A28" s="49">
+        <v>45775</v>
+      </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1159,11 +4580,17 @@
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="3"/>
-      <c r="O28" s="33"/>
+      <c r="K28" s="47"/>
+      <c r="O28" s="4"/>
+      <c r="W28" s="117"/>
+      <c r="X28" s="117"/>
+      <c r="Y28" s="117"/>
+      <c r="Z28" s="117"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45776</v>
+      </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1173,11 +4600,17 @@
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="3"/>
-      <c r="O29" s="33"/>
+      <c r="K29" s="47"/>
+      <c r="O29" s="4"/>
+      <c r="W29" s="117"/>
+      <c r="X29" s="117"/>
+      <c r="Y29" s="117"/>
+      <c r="Z29" s="117"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>45777</v>
+      </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1187,11 +4620,17 @@
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="3"/>
-      <c r="O30" s="33"/>
+      <c r="K30" s="47"/>
+      <c r="O30" s="4"/>
+      <c r="W30" s="117"/>
+      <c r="X30" s="117"/>
+      <c r="Y30" s="117"/>
+      <c r="Z30" s="117"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>45778</v>
+      </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1201,10 +4640,14 @@
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-      <c r="K31" s="3"/>
-      <c r="O31" s="33"/>
+      <c r="K31" s="47"/>
+      <c r="O31" s="4"/>
+      <c r="W31" s="117"/>
+      <c r="X31" s="117"/>
+      <c r="Y31" s="117"/>
+      <c r="Z31" s="117"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1215,10 +4658,14 @@
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="3"/>
-      <c r="O32" s="33"/>
+      <c r="K32" s="47"/>
+      <c r="O32" s="4"/>
+      <c r="W32" s="117"/>
+      <c r="X32" s="117"/>
+      <c r="Y32" s="117"/>
+      <c r="Z32" s="117"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1229,10 +4676,14 @@
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="3"/>
-      <c r="O33" s="33"/>
+      <c r="K33" s="47"/>
+      <c r="O33" s="4"/>
+      <c r="W33" s="117"/>
+      <c r="X33" s="117"/>
+      <c r="Y33" s="117"/>
+      <c r="Z33" s="117"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1243,10 +4694,10 @@
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="3"/>
-      <c r="O34" s="33"/>
+      <c r="K34" s="47"/>
+      <c r="O34" s="4"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1257,10 +4708,10 @@
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="3"/>
-      <c r="O35" s="33"/>
+      <c r="K35" s="47"/>
+      <c r="O35" s="4"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1271,10 +4722,10 @@
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="3"/>
-      <c r="O36" s="33"/>
+      <c r="K36" s="47"/>
+      <c r="O36" s="4"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1285,10 +4736,10 @@
       <c r="H37" s="3"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
-      <c r="K37" s="3"/>
-      <c r="O37" s="33"/>
+      <c r="K37" s="47"/>
+      <c r="O37" s="4"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1299,14 +4750,18 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="47"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="O39" s="4"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S11:U20">
+    <sortCondition descending="1" ref="U11:U20"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>